--- a/plate3d/PLATE3D_XWING.xlsx
+++ b/plate3d/PLATE3D_XWING.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="65">
   <si>
     <t>X-wing - PLATE3D demo</t>
   </si>
@@ -52,16 +52,25 @@
     <t>PLATE</t>
   </si>
   <si>
-    <t>pl.fus</t>
+    <t>pl.rear</t>
   </si>
   <si>
     <t>ALLOY</t>
   </si>
   <si>
+    <t>RECT</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>pl.nose.lo</t>
+  </si>
+  <si>
     <t>TRAP</t>
   </si>
   <si>
-    <t>bc</t>
+    <t>pl.nose.up</t>
   </si>
   <si>
     <t>pl.cock</t>
@@ -94,6 +103,9 @@
     <t>bar.muz</t>
   </si>
   <si>
+    <t>bar.ndl</t>
+  </si>
+  <si>
     <t>bar.r2</t>
   </si>
   <si>
@@ -119,6 +131,12 @@
   </si>
   <si>
     <t>ROT.X</t>
+  </si>
+  <si>
+    <t>ROT.Y</t>
+  </si>
+  <si>
+    <t>ROT.Z</t>
   </si>
   <si>
     <t>body wedge, canopy, droid</t>
@@ -581,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -625,7 +643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -639,7 +657,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -648,16 +666,10 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="I2">
-        <v>380</v>
-      </c>
-      <c r="J2">
-        <v>80</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -674,22 +686,22 @@
         <v>14</v>
       </c>
       <c r="E3">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
       </c>
       <c r="H3">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="I3">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>400</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -703,91 +715,121 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
         <v>16</v>
       </c>
       <c r="H4">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="I4">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>290</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>72</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>190</v>
+      </c>
+      <c r="I5">
+        <v>95</v>
+      </c>
+      <c r="J5">
+        <v>42</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>220</v>
+      </c>
+      <c r="I6">
         <v>130</v>
       </c>
-      <c r="J4">
+      <c r="J6">
         <v>280</v>
       </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>80</v>
-      </c>
-      <c r="F7">
-        <v>240</v>
+      <c r="K6">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>16</v>
-      </c>
-      <c r="F8">
-        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -795,19 +837,19 @@
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="F9">
-        <v>60</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -815,476 +857,647 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>34</v>
+      </c>
+      <c r="F13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F10">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C15" t="s">
         <v>2</v>
       </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c r="I12" t="s">
+      <c r="E15" t="s">
         <v>34</v>
       </c>
-      <c r="J12" t="s">
+      <c r="F15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="G15" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="H15" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="I15" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
+      <c r="J15" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
         <v>13</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E16" t="s">
         <v>16</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>-40</v>
-      </c>
-      <c r="I13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F16">
+        <v>-140</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>-42.5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
         <v>17</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E17" t="s">
         <v>16</v>
       </c>
-      <c r="F14">
-        <v>20</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>40</v>
-      </c>
-      <c r="I14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15">
-        <v>-110</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>40</v>
-      </c>
-      <c r="I15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="F17">
+        <v>70</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>-21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" t="s">
-        <v>33</v>
+      <c r="F18">
+        <v>70</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>16.5</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>-90</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19">
+        <v>95</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>42.5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20">
+        <v>-90</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>42.5</v>
+      </c>
+      <c r="I20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" t="s">
         <v>37</v>
       </c>
-      <c r="C19" t="s">
+      <c r="I23" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19">
-        <v>-180</v>
-      </c>
-      <c r="G19">
-        <v>72</v>
-      </c>
-      <c r="H19">
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>-330</v>
+      </c>
+      <c r="G24">
+        <v>78</v>
+      </c>
+      <c r="H24">
+        <v>62</v>
+      </c>
+      <c r="I24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>-190</v>
+      </c>
+      <c r="G25">
+        <v>123</v>
+      </c>
+      <c r="H25">
+        <v>62</v>
+      </c>
+      <c r="I25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>-220</v>
+      </c>
+      <c r="G26">
+        <v>386.1</v>
+      </c>
+      <c r="H26">
+        <v>157.8</v>
+      </c>
+      <c r="I26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>45</v>
+      </c>
+      <c r="G27">
+        <v>386.1</v>
+      </c>
+      <c r="H27">
+        <v>157.8</v>
+      </c>
+      <c r="I27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
+        <v>386.1</v>
+      </c>
+      <c r="H28">
+        <v>157.8</v>
+      </c>
+      <c r="I28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I19" t="s">
+      <c r="B32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20">
-        <v>-60</v>
-      </c>
-      <c r="G20">
-        <v>112</v>
-      </c>
-      <c r="H20">
-        <v>58</v>
-      </c>
-      <c r="I20" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21">
-        <v>-130</v>
-      </c>
-      <c r="G21">
-        <v>375.1</v>
-      </c>
-      <c r="H21">
-        <v>153.8</v>
-      </c>
-      <c r="I21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22">
-        <v>170</v>
-      </c>
-      <c r="G22">
-        <v>375.1</v>
-      </c>
-      <c r="H22">
-        <v>153.8</v>
-      </c>
-      <c r="I22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34">
+        <v>-330</v>
+      </c>
+      <c r="G34">
+        <v>78</v>
+      </c>
+      <c r="H34">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="s">
         <v>46</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28">
-        <v>-180</v>
-      </c>
-      <c r="G28">
-        <v>72</v>
-      </c>
-      <c r="H28">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" t="s">
-        <v>57</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>58</v>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_XWING.xlsx
+++ b/plate3d/PLATE3D_XWING.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="72">
   <si>
     <t>X-wing - PLATE3D demo</t>
   </si>
@@ -203,6 +203,27 @@
   </si>
   <si>
     <t>MIR</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>XWING - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -599,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -812,6 +833,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
@@ -932,6 +954,7 @@
         <v>26</v>
       </c>
     </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
@@ -1153,6 +1176,7 @@
         <v>16</v>
       </c>
     </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
@@ -1353,6 +1377,7 @@
         <v>51</v>
       </c>
     </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>11</v>
@@ -1408,6 +1433,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
@@ -1492,16 +1518,51 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="3" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38">
+        <v>50</v>
+      </c>
+      <c r="H38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_XWING.xlsx
+++ b/plate3d/PLATE3D_XWING.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="65">
   <si>
     <t>X-wing - PLATE3D demo</t>
   </si>
@@ -203,27 +203,6 @@
   </si>
   <si>
     <t>MIR</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>XWING - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
   </si>
   <si>
     <t>END</t>
@@ -620,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -833,7 +812,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
@@ -954,7 +932,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
@@ -1176,7 +1153,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>11</v>
@@ -1377,7 +1353,6 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>11</v>
@@ -1433,7 +1408,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25"/>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>11</v>
@@ -1518,51 +1492,16 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" t="s">
-        <v>65</v>
-      </c>
-      <c r="G38">
-        <v>50</v>
-      </c>
-      <c r="H38" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>